--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/BonusCalist.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/BonusCalist.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28130" windowHeight="12540"/>
   </bookViews>
@@ -21,12 +26,6 @@
     <t>销售代码（子产品代码）</t>
   </si>
   <si>
-    <t>净值</t>
-  </si>
-  <si>
-    <t>份额</t>
-  </si>
-  <si>
     <t>单位净值</t>
   </si>
   <si>
@@ -66,6 +65,14 @@
   </si>
   <si>
     <t>收益率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品期末余额（份额）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品资产净值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -127,7 +134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -144,6 +151,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -425,7 +444,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="21.25" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="2"/>
+    <col min="2" max="4" width="9" style="2"/>
+    <col min="5" max="6" width="9" style="7"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="46" customHeight="1">
@@ -433,52 +454,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="9"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
